--- a/data/White Mulberry/Mar/business_report.xlsx
+++ b/data/White Mulberry/Mar/business_report.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projects\buybox\data\White Mulberry\Mar\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A6C53BD-A846-43A1-B12B-64BD865038AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1FF3B7A-975F-424E-8668-FCEF35ED0308}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$W$38</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$W$1</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="159">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="169">
   <si>
     <t>(Parent) ASIN</t>
   </si>
@@ -426,18 +426,9 @@
     <t>FBA79175</t>
   </si>
   <si>
-    <t>WM-LODN-BK</t>
-  </si>
-  <si>
-    <t>FBA79789</t>
-  </si>
-  <si>
     <t>TVMF1ML</t>
   </si>
   <si>
-    <t>FBA79788</t>
-  </si>
-  <si>
     <t>TVCT1ML</t>
   </si>
   <si>
@@ -447,9 +438,6 @@
     <t>VLMS1ML</t>
   </si>
   <si>
-    <t>FBA79787</t>
-  </si>
-  <si>
     <t>TVCF1ML</t>
   </si>
   <si>
@@ -459,9 +447,6 @@
     <t>WM-HA2M-BK</t>
   </si>
   <si>
-    <t>FBA79791</t>
-  </si>
-  <si>
     <t>TVFM1ML</t>
   </si>
   <si>
@@ -477,9 +462,6 @@
     <t>WM-HA1M-BK</t>
   </si>
   <si>
-    <t>FBA79786</t>
-  </si>
-  <si>
     <t>POSS-01</t>
   </si>
   <si>
@@ -501,16 +483,64 @@
     <t>TVLF1ML</t>
   </si>
   <si>
-    <t>FBA79784</t>
-  </si>
-  <si>
     <t>POS2M</t>
   </si>
   <si>
-    <t>FBA79785</t>
-  </si>
-  <si>
     <t>POS2MK</t>
+  </si>
+  <si>
+    <t>WM-SMD09-WH</t>
+  </si>
+  <si>
+    <t>B0FFNDKXZY</t>
+  </si>
+  <si>
+    <t>White Mulberry L Shaped Desk Variation (JW)</t>
+  </si>
+  <si>
+    <t>B0FG8FQ3Q1</t>
+  </si>
+  <si>
+    <t>White Mulberry</t>
+  </si>
+  <si>
+    <t>B0F1YW1R2Y</t>
+  </si>
+  <si>
+    <t>White Mulberry Monitor Arm Variation</t>
+  </si>
+  <si>
+    <t>FBK79789</t>
+  </si>
+  <si>
+    <t>FBK79788</t>
+  </si>
+  <si>
+    <t>FBK79787</t>
+  </si>
+  <si>
+    <t>FBK79791</t>
+  </si>
+  <si>
+    <t>FBK79786</t>
+  </si>
+  <si>
+    <t>FBK79784</t>
+  </si>
+  <si>
+    <t>B0F1YXYNM6</t>
+  </si>
+  <si>
+    <t>White Mulberry Monitor Stand Variation</t>
+  </si>
+  <si>
+    <t>FBK79785</t>
+  </si>
+  <si>
+    <t>B0FNR244QP</t>
+  </si>
+  <si>
+    <t>White Mulberry TV Wall Mount Variation</t>
   </si>
 </sst>
 </file>
@@ -879,7 +909,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:W38"/>
+  <dimension ref="A1:W44"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:23" x14ac:dyDescent="0.3">
@@ -955,354 +985,354 @@
     </row>
     <row r="2" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="B2" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="C2" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D2" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E2" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="F2" s="4">
-        <v>5875</v>
+        <v>19578</v>
       </c>
       <c r="G2">
-        <v>272</v>
+        <v>493</v>
       </c>
       <c r="H2" s="2">
-        <v>8.3000000000000001E-3</v>
+        <v>0.3014</v>
       </c>
       <c r="I2" s="2">
-        <v>1.9699999999999999E-2</v>
+        <v>0.26029999999999998</v>
       </c>
       <c r="J2" s="4">
-        <v>8037</v>
+        <v>27743</v>
       </c>
       <c r="K2">
-        <v>358</v>
+        <v>695</v>
       </c>
       <c r="L2" s="2">
-        <v>8.3999999999999995E-3</v>
+        <v>0.30959999999999999</v>
       </c>
       <c r="M2" s="2">
-        <v>1.8599999999999998E-2</v>
+        <v>0.26669999999999999</v>
       </c>
       <c r="N2" s="2">
-        <v>2.0999999999999999E-3</v>
+        <v>0.82630000000000003</v>
       </c>
       <c r="O2" s="2">
-        <v>4.0000000000000001E-3</v>
+        <v>0.92310000000000003</v>
       </c>
       <c r="P2">
-        <v>0</v>
+        <v>131</v>
       </c>
       <c r="Q2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R2" s="2">
-        <v>0</v>
+        <v>6.7000000000000002E-3</v>
       </c>
       <c r="S2" s="2">
-        <v>0</v>
-      </c>
-      <c r="T2">
-        <v>0</v>
+        <v>8.0999999999999996E-3</v>
+      </c>
+      <c r="T2" s="3">
+        <v>870334.75423728814</v>
       </c>
       <c r="U2" s="3">
-        <v>0</v>
+        <v>33215.01</v>
       </c>
       <c r="V2">
-        <v>0</v>
+        <v>131</v>
       </c>
       <c r="W2">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="B3" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="C3" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="D3" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="E3" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F3" s="4">
-        <v>1595</v>
+        <v>4592</v>
       </c>
       <c r="G3">
-        <v>122</v>
+        <v>254</v>
       </c>
       <c r="H3" s="2">
-        <v>2.2000000000000001E-3</v>
+        <v>7.0699999999999999E-2</v>
       </c>
       <c r="I3" s="2">
-        <v>8.8000000000000005E-3</v>
+        <v>0.1341</v>
       </c>
       <c r="J3" s="4">
-        <v>2072</v>
+        <v>6511</v>
       </c>
       <c r="K3">
-        <v>154</v>
+        <v>361</v>
       </c>
       <c r="L3" s="2">
-        <v>2.2000000000000001E-3</v>
+        <v>7.2599999999999998E-2</v>
       </c>
       <c r="M3" s="2">
-        <v>8.0000000000000002E-3</v>
+        <v>0.13850000000000001</v>
       </c>
       <c r="N3" s="2">
-        <v>2.2000000000000001E-3</v>
+        <v>0.78129999999999999</v>
       </c>
       <c r="O3" s="2">
-        <v>9.5999999999999992E-3</v>
+        <v>1</v>
       </c>
       <c r="P3">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="Q3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R3" s="2">
-        <v>0</v>
+        <v>5.8999999999999999E-3</v>
       </c>
       <c r="S3" s="2">
-        <v>0</v>
-      </c>
-      <c r="T3">
-        <v>0</v>
+        <v>7.9000000000000008E-3</v>
+      </c>
+      <c r="T3" s="3">
+        <v>191319.50847457626</v>
       </c>
       <c r="U3" s="3">
-        <v>0</v>
+        <v>16531.02</v>
       </c>
       <c r="V3">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="W3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="B4" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="C4" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D4" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="E4" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F4" s="4">
-        <v>19578</v>
+        <v>3766</v>
       </c>
       <c r="G4">
-        <v>493</v>
+        <v>185</v>
       </c>
       <c r="H4" s="2">
-        <v>0.3014</v>
+        <v>5.8000000000000003E-2</v>
       </c>
       <c r="I4" s="2">
-        <v>0.26029999999999998</v>
+        <v>9.7699999999999995E-2</v>
       </c>
       <c r="J4" s="4">
-        <v>27743</v>
+        <v>5063</v>
       </c>
       <c r="K4">
-        <v>695</v>
+        <v>253</v>
       </c>
       <c r="L4" s="2">
-        <v>0.30959999999999999</v>
+        <v>5.6500000000000002E-2</v>
       </c>
       <c r="M4" s="2">
-        <v>0.26669999999999999</v>
+        <v>9.7100000000000006E-2</v>
       </c>
       <c r="N4" s="2">
-        <v>0.82630000000000003</v>
+        <v>0.34639999999999999</v>
       </c>
       <c r="O4" s="2">
-        <v>0.92310000000000003</v>
+        <v>0.99439999999999995</v>
       </c>
       <c r="P4">
-        <v>131</v>
+        <v>18</v>
       </c>
       <c r="Q4">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R4" s="2">
-        <v>6.7000000000000002E-3</v>
+        <v>4.7999999999999996E-3</v>
       </c>
       <c r="S4" s="2">
-        <v>8.0999999999999996E-3</v>
-      </c>
-      <c r="T4">
-        <v>870334.75423728814</v>
+        <v>0</v>
+      </c>
+      <c r="T4" s="3">
+        <v>121002.54237288136</v>
       </c>
       <c r="U4" s="3">
-        <v>33215.01</v>
+        <v>0</v>
       </c>
       <c r="V4">
-        <v>131</v>
+        <v>18</v>
       </c>
       <c r="W4">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="B5" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="C5" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="D5" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="E5" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="F5" s="4">
-        <v>4592</v>
+        <v>2261</v>
       </c>
       <c r="G5">
-        <v>254</v>
+        <v>86</v>
       </c>
       <c r="H5" s="2">
-        <v>7.0699999999999999E-2</v>
+        <v>3.4799999999999998E-2</v>
       </c>
       <c r="I5" s="2">
-        <v>0.1341</v>
+        <v>4.5400000000000003E-2</v>
       </c>
       <c r="J5" s="4">
-        <v>6511</v>
+        <v>3062</v>
       </c>
       <c r="K5">
-        <v>361</v>
+        <v>135</v>
       </c>
       <c r="L5" s="2">
-        <v>7.2599999999999998E-2</v>
+        <v>3.4200000000000001E-2</v>
       </c>
       <c r="M5" s="2">
-        <v>0.13850000000000001</v>
+        <v>5.1799999999999999E-2</v>
       </c>
       <c r="N5" s="2">
-        <v>0.78129999999999999</v>
+        <v>0.50019999999999998</v>
       </c>
       <c r="O5" s="2">
         <v>1</v>
       </c>
       <c r="P5">
-        <v>27</v>
+        <v>8</v>
       </c>
       <c r="Q5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R5" s="2">
-        <v>5.8999999999999999E-3</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="S5" s="2">
-        <v>7.9000000000000008E-3</v>
-      </c>
-      <c r="T5">
-        <v>191319.50847457626</v>
+        <v>1.1599999999999999E-2</v>
+      </c>
+      <c r="T5" s="3">
+        <v>88018.652542372874</v>
       </c>
       <c r="U5" s="3">
-        <v>16531.02</v>
+        <v>12869.01</v>
       </c>
       <c r="V5">
-        <v>27</v>
+        <v>8</v>
       </c>
       <c r="W5">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="B6" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="C6" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D6" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="E6" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F6" s="4">
-        <v>3766</v>
+        <v>1173</v>
       </c>
       <c r="G6">
-        <v>185</v>
+        <v>73</v>
       </c>
       <c r="H6" s="2">
-        <v>5.8000000000000003E-2</v>
+        <v>1.8100000000000002E-2</v>
       </c>
       <c r="I6" s="2">
-        <v>9.7699999999999995E-2</v>
+        <v>3.85E-2</v>
       </c>
       <c r="J6" s="4">
-        <v>5063</v>
+        <v>1494</v>
       </c>
       <c r="K6">
-        <v>253</v>
+        <v>87</v>
       </c>
       <c r="L6" s="2">
-        <v>5.6500000000000002E-2</v>
+        <v>1.67E-2</v>
       </c>
       <c r="M6" s="2">
-        <v>9.7100000000000006E-2</v>
+        <v>3.3399999999999999E-2</v>
       </c>
       <c r="N6" s="2">
-        <v>0.34639999999999999</v>
+        <v>0.60589999999999999</v>
       </c>
       <c r="O6" s="2">
-        <v>0.99439999999999995</v>
+        <v>1</v>
       </c>
       <c r="P6">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="Q6">
         <v>0</v>
       </c>
       <c r="R6" s="2">
-        <v>4.7999999999999996E-3</v>
+        <v>6.0000000000000001E-3</v>
       </c>
       <c r="S6" s="2">
         <v>0</v>
       </c>
-      <c r="T6">
-        <v>121002.54237288136</v>
+      <c r="T6" s="3">
+        <v>49824.576271186445</v>
       </c>
       <c r="U6" s="3">
         <v>0</v>
       </c>
       <c r="V6">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="W6">
         <v>0</v>
@@ -1310,70 +1340,70 @@
     </row>
     <row r="7" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="B7" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="C7" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="D7" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="E7" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="F7" s="4">
-        <v>2261</v>
+        <v>1006</v>
       </c>
       <c r="G7">
-        <v>86</v>
+        <v>47</v>
       </c>
       <c r="H7" s="2">
-        <v>3.4799999999999998E-2</v>
+        <v>1.55E-2</v>
       </c>
       <c r="I7" s="2">
-        <v>4.5400000000000003E-2</v>
+        <v>2.4799999999999999E-2</v>
       </c>
       <c r="J7" s="4">
-        <v>3062</v>
+        <v>1244</v>
       </c>
       <c r="K7">
-        <v>135</v>
+        <v>56</v>
       </c>
       <c r="L7" s="2">
-        <v>3.4200000000000001E-2</v>
+        <v>1.3899999999999999E-2</v>
       </c>
       <c r="M7" s="2">
-        <v>5.1799999999999999E-2</v>
+        <v>2.1499999999999998E-2</v>
       </c>
       <c r="N7" s="2">
-        <v>0.50019999999999998</v>
+        <v>0.63129999999999997</v>
       </c>
       <c r="O7" s="2">
         <v>1</v>
       </c>
       <c r="P7">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Q7">
         <v>1</v>
       </c>
       <c r="R7" s="2">
-        <v>3.5000000000000001E-3</v>
+        <v>7.0000000000000001E-3</v>
       </c>
       <c r="S7" s="2">
-        <v>1.1599999999999999E-2</v>
-      </c>
-      <c r="T7">
-        <v>88018.652542372874</v>
+        <v>2.1299999999999999E-2</v>
+      </c>
+      <c r="T7" s="3">
+        <v>91521.186440677964</v>
       </c>
       <c r="U7" s="3">
-        <v>12869.01</v>
+        <v>15001</v>
       </c>
       <c r="V7">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W7">
         <v>1</v>
@@ -1381,141 +1411,141 @@
     </row>
     <row r="8" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="B8" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="C8" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="D8" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="E8" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="F8" s="4">
-        <v>1173</v>
+        <v>2979</v>
       </c>
       <c r="G8">
-        <v>73</v>
+        <v>115</v>
       </c>
       <c r="H8" s="2">
-        <v>1.8100000000000002E-2</v>
+        <v>4.5900000000000003E-2</v>
       </c>
       <c r="I8" s="2">
-        <v>3.85E-2</v>
+        <v>6.0699999999999997E-2</v>
       </c>
       <c r="J8" s="4">
-        <v>1494</v>
+        <v>3904</v>
       </c>
       <c r="K8">
-        <v>87</v>
+        <v>174</v>
       </c>
       <c r="L8" s="2">
-        <v>1.67E-2</v>
+        <v>4.36E-2</v>
       </c>
       <c r="M8" s="2">
-        <v>3.3399999999999999E-2</v>
+        <v>6.6799999999999998E-2</v>
       </c>
       <c r="N8" s="2">
-        <v>0.60589999999999999</v>
+        <v>0.66369999999999996</v>
       </c>
       <c r="O8" s="2">
-        <v>1</v>
+        <v>0.99070000000000003</v>
       </c>
       <c r="P8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Q8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R8" s="2">
-        <v>6.0000000000000001E-3</v>
+        <v>2E-3</v>
       </c>
       <c r="S8" s="2">
-        <v>0</v>
-      </c>
-      <c r="T8">
-        <v>49824.576271186445</v>
+        <v>8.6999999999999994E-3</v>
+      </c>
+      <c r="T8" s="3">
+        <v>77120.338983050853</v>
       </c>
       <c r="U8" s="3">
-        <v>0</v>
+        <v>15001</v>
       </c>
       <c r="V8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W8">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="B9" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="C9" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="D9" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="E9" t="s">
-        <v>36</v>
-      </c>
-      <c r="F9" s="4">
-        <v>1006</v>
+        <v>40</v>
+      </c>
+      <c r="F9">
+        <v>765</v>
       </c>
       <c r="G9">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="H9" s="2">
-        <v>1.55E-2</v>
+        <v>1.18E-2</v>
       </c>
       <c r="I9" s="2">
-        <v>2.4799999999999999E-2</v>
-      </c>
-      <c r="J9" s="4">
-        <v>1244</v>
+        <v>2.69E-2</v>
+      </c>
+      <c r="J9">
+        <v>961</v>
       </c>
       <c r="K9">
-        <v>56</v>
+        <v>73</v>
       </c>
       <c r="L9" s="2">
-        <v>1.3899999999999999E-2</v>
+        <v>1.0699999999999999E-2</v>
       </c>
       <c r="M9" s="2">
-        <v>2.1499999999999998E-2</v>
+        <v>2.8000000000000001E-2</v>
       </c>
       <c r="N9" s="2">
-        <v>0.63129999999999997</v>
+        <v>0.75339999999999996</v>
       </c>
       <c r="O9" s="2">
         <v>1</v>
       </c>
       <c r="P9">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Q9">
         <v>1</v>
       </c>
       <c r="R9" s="2">
-        <v>7.0000000000000001E-3</v>
+        <v>6.4999999999999997E-3</v>
       </c>
       <c r="S9" s="2">
-        <v>2.1299999999999999E-2</v>
-      </c>
-      <c r="T9">
-        <v>91521.186440677964</v>
+        <v>1.9599999999999999E-2</v>
+      </c>
+      <c r="T9" s="3">
+        <v>35517.805084745763</v>
       </c>
       <c r="U9" s="3">
-        <v>15001</v>
+        <v>8315.01</v>
       </c>
       <c r="V9">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="W9">
         <v>1</v>
@@ -1523,70 +1553,70 @@
     </row>
     <row r="10" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="B10" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="C10" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="D10" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="E10" t="s">
-        <v>38</v>
-      </c>
-      <c r="F10" s="4">
-        <v>2979</v>
+        <v>42</v>
+      </c>
+      <c r="F10">
+        <v>455</v>
       </c>
       <c r="G10">
-        <v>115</v>
+        <v>27</v>
       </c>
       <c r="H10" s="2">
-        <v>4.5900000000000003E-2</v>
+        <v>7.0000000000000001E-3</v>
       </c>
       <c r="I10" s="2">
-        <v>6.0699999999999997E-2</v>
-      </c>
-      <c r="J10" s="4">
-        <v>3904</v>
+        <v>1.43E-2</v>
+      </c>
+      <c r="J10">
+        <v>612</v>
       </c>
       <c r="K10">
-        <v>174</v>
+        <v>43</v>
       </c>
       <c r="L10" s="2">
-        <v>4.36E-2</v>
+        <v>6.7999999999999996E-3</v>
       </c>
       <c r="M10" s="2">
-        <v>6.6799999999999998E-2</v>
+        <v>1.6500000000000001E-2</v>
       </c>
       <c r="N10" s="2">
-        <v>0.66369999999999996</v>
+        <v>0.9163</v>
       </c>
       <c r="O10" s="2">
-        <v>0.99070000000000003</v>
+        <v>0.96970000000000001</v>
       </c>
       <c r="P10">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Q10">
         <v>1</v>
       </c>
       <c r="R10" s="2">
-        <v>2E-3</v>
+        <v>1.0999999999999999E-2</v>
       </c>
       <c r="S10" s="2">
-        <v>8.6999999999999994E-3</v>
-      </c>
-      <c r="T10">
-        <v>77120.338983050853</v>
+        <v>3.6999999999999998E-2</v>
+      </c>
+      <c r="T10" s="3">
+        <v>64696.618644067792</v>
       </c>
       <c r="U10" s="3">
-        <v>15001</v>
+        <v>15146.01</v>
       </c>
       <c r="V10">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W10">
         <v>1</v>
@@ -1594,46 +1624,46 @@
     </row>
     <row r="11" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="B11" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="C11" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="D11" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="E11" t="s">
-        <v>40</v>
-      </c>
-      <c r="F11">
-        <v>765</v>
+        <v>44</v>
+      </c>
+      <c r="F11" s="4">
+        <v>1321</v>
       </c>
       <c r="G11">
-        <v>51</v>
+        <v>87</v>
       </c>
       <c r="H11" s="2">
-        <v>1.18E-2</v>
+        <v>2.0299999999999999E-2</v>
       </c>
       <c r="I11" s="2">
-        <v>2.69E-2</v>
-      </c>
-      <c r="J11">
-        <v>961</v>
+        <v>4.5900000000000003E-2</v>
+      </c>
+      <c r="J11" s="4">
+        <v>1779</v>
       </c>
       <c r="K11">
-        <v>73</v>
+        <v>99</v>
       </c>
       <c r="L11" s="2">
-        <v>1.0699999999999999E-2</v>
+        <v>1.9800000000000002E-2</v>
       </c>
       <c r="M11" s="2">
-        <v>2.8000000000000001E-2</v>
+        <v>3.7999999999999999E-2</v>
       </c>
       <c r="N11" s="2">
-        <v>0.75339999999999996</v>
+        <v>0.56910000000000005</v>
       </c>
       <c r="O11" s="2">
         <v>1</v>
@@ -1645,16 +1675,16 @@
         <v>1</v>
       </c>
       <c r="R11" s="2">
-        <v>6.4999999999999997E-3</v>
+        <v>3.8E-3</v>
       </c>
       <c r="S11" s="2">
-        <v>1.9599999999999999E-2</v>
-      </c>
-      <c r="T11">
-        <v>35517.805084745763</v>
+        <v>1.15E-2</v>
+      </c>
+      <c r="T11" s="3">
+        <v>54970.347457627126</v>
       </c>
       <c r="U11" s="3">
-        <v>8315.01</v>
+        <v>12869.01</v>
       </c>
       <c r="V11">
         <v>5</v>
@@ -1665,283 +1695,283 @@
     </row>
     <row r="12" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="B12" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="C12" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="D12" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="E12" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="F12">
-        <v>455</v>
+        <v>258</v>
       </c>
       <c r="G12">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="H12" s="2">
-        <v>7.0000000000000001E-3</v>
+        <v>4.0000000000000001E-3</v>
       </c>
       <c r="I12" s="2">
-        <v>1.43E-2</v>
+        <v>1.1599999999999999E-2</v>
       </c>
       <c r="J12">
-        <v>612</v>
+        <v>362</v>
       </c>
       <c r="K12">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="L12" s="2">
-        <v>6.7999999999999996E-3</v>
+        <v>4.0000000000000001E-3</v>
       </c>
       <c r="M12" s="2">
-        <v>1.6500000000000001E-2</v>
+        <v>1.23E-2</v>
       </c>
       <c r="N12" s="2">
-        <v>0.9163</v>
+        <v>0.63849999999999996</v>
       </c>
       <c r="O12" s="2">
-        <v>0.96970000000000001</v>
+        <v>0.96550000000000002</v>
       </c>
       <c r="P12">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R12" s="2">
-        <v>1.0999999999999999E-2</v>
+        <v>1.55E-2</v>
       </c>
       <c r="S12" s="2">
-        <v>3.6999999999999998E-2</v>
-      </c>
-      <c r="T12">
-        <v>64696.618644067792</v>
+        <v>0</v>
+      </c>
+      <c r="T12" s="3">
+        <v>47454.237288135599</v>
       </c>
       <c r="U12" s="3">
-        <v>15146.01</v>
+        <v>0</v>
       </c>
       <c r="V12">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="W12">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="B13" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="C13" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="D13" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="E13" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="F13" s="4">
-        <v>1321</v>
+        <v>1692</v>
       </c>
       <c r="G13">
-        <v>87</v>
+        <v>45</v>
       </c>
       <c r="H13" s="2">
-        <v>2.0299999999999999E-2</v>
+        <v>2.5999999999999999E-2</v>
       </c>
       <c r="I13" s="2">
-        <v>4.5900000000000003E-2</v>
+        <v>2.3800000000000002E-2</v>
       </c>
       <c r="J13" s="4">
-        <v>1779</v>
+        <v>2259</v>
       </c>
       <c r="K13">
-        <v>99</v>
+        <v>54</v>
       </c>
       <c r="L13" s="2">
-        <v>1.9800000000000002E-2</v>
+        <v>2.52E-2</v>
       </c>
       <c r="M13" s="2">
-        <v>3.7999999999999999E-2</v>
+        <v>2.07E-2</v>
       </c>
       <c r="N13" s="2">
-        <v>0.56910000000000005</v>
+        <v>0.46750000000000003</v>
       </c>
       <c r="O13" s="2">
         <v>1</v>
       </c>
       <c r="P13">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="Q13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R13" s="2">
-        <v>3.8E-3</v>
+        <v>1.8E-3</v>
       </c>
       <c r="S13" s="2">
-        <v>1.15E-2</v>
-      </c>
-      <c r="T13">
-        <v>54970.347457627126</v>
+        <v>0</v>
+      </c>
+      <c r="T13" s="3">
+        <v>33048.305084745763</v>
       </c>
       <c r="U13" s="3">
-        <v>12869.01</v>
+        <v>0</v>
       </c>
       <c r="V13">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="W13">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="B14" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="C14" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="D14" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="E14" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="F14">
-        <v>258</v>
+        <v>314</v>
       </c>
       <c r="G14">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="H14" s="2">
-        <v>4.0000000000000001E-3</v>
+        <v>4.7999999999999996E-3</v>
       </c>
       <c r="I14" s="2">
-        <v>1.1599999999999999E-2</v>
+        <v>1.6400000000000001E-2</v>
       </c>
       <c r="J14">
-        <v>362</v>
+        <v>382</v>
       </c>
       <c r="K14">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="L14" s="2">
-        <v>4.0000000000000001E-3</v>
+        <v>4.3E-3</v>
       </c>
       <c r="M14" s="2">
-        <v>1.23E-2</v>
+        <v>1.6899999999999998E-2</v>
       </c>
       <c r="N14" s="2">
-        <v>0.63849999999999996</v>
+        <v>0.60240000000000005</v>
       </c>
       <c r="O14" s="2">
-        <v>0.96550000000000002</v>
+        <v>1</v>
       </c>
       <c r="P14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Q14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R14" s="2">
-        <v>1.55E-2</v>
+        <v>6.4000000000000003E-3</v>
       </c>
       <c r="S14" s="2">
-        <v>0</v>
-      </c>
-      <c r="T14">
-        <v>47454.237288135599</v>
+        <v>3.2300000000000002E-2</v>
+      </c>
+      <c r="T14" s="3">
+        <v>21922.042372881355</v>
       </c>
       <c r="U14" s="3">
-        <v>0</v>
+        <v>12869.01</v>
       </c>
       <c r="V14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="W14">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="B15" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="C15" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="D15" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="E15" t="s">
-        <v>48</v>
-      </c>
-      <c r="F15" s="4">
-        <v>1692</v>
+        <v>52</v>
+      </c>
+      <c r="F15">
+        <v>113</v>
       </c>
       <c r="G15">
-        <v>45</v>
+        <v>3</v>
       </c>
       <c r="H15" s="2">
-        <v>2.5999999999999999E-2</v>
+        <v>1.6999999999999999E-3</v>
       </c>
       <c r="I15" s="2">
-        <v>2.3800000000000002E-2</v>
-      </c>
-      <c r="J15" s="4">
-        <v>2259</v>
+        <v>1.6000000000000001E-3</v>
+      </c>
+      <c r="J15">
+        <v>164</v>
       </c>
       <c r="K15">
-        <v>54</v>
+        <v>3</v>
       </c>
       <c r="L15" s="2">
-        <v>2.52E-2</v>
+        <v>1.8E-3</v>
       </c>
       <c r="M15" s="2">
-        <v>2.07E-2</v>
+        <v>1.1999999999999999E-3</v>
       </c>
       <c r="N15" s="2">
-        <v>0.46750000000000003</v>
+        <v>0.86899999999999999</v>
       </c>
       <c r="O15" s="2">
         <v>1</v>
       </c>
       <c r="P15">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Q15">
         <v>0</v>
       </c>
       <c r="R15" s="2">
-        <v>1.8E-3</v>
+        <v>8.8000000000000005E-3</v>
       </c>
       <c r="S15" s="2">
         <v>0</v>
       </c>
-      <c r="T15">
-        <v>33048.305084745763</v>
+      <c r="T15" s="3">
+        <v>10168.644067796611</v>
       </c>
       <c r="U15" s="3">
         <v>0</v>
       </c>
       <c r="V15">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="W15">
         <v>0</v>
@@ -1949,117 +1979,117 @@
     </row>
     <row r="16" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="B16" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="C16" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="D16" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="E16" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="F16">
-        <v>314</v>
+        <v>41</v>
       </c>
       <c r="G16">
-        <v>31</v>
+        <v>10</v>
       </c>
       <c r="H16" s="2">
-        <v>4.7999999999999996E-3</v>
+        <v>5.9999999999999995E-4</v>
       </c>
       <c r="I16" s="2">
-        <v>1.6400000000000001E-2</v>
+        <v>5.3E-3</v>
       </c>
       <c r="J16">
-        <v>382</v>
+        <v>67</v>
       </c>
       <c r="K16">
-        <v>44</v>
+        <v>17</v>
       </c>
       <c r="L16" s="2">
-        <v>4.3E-3</v>
+        <v>6.9999999999999999E-4</v>
       </c>
       <c r="M16" s="2">
-        <v>1.6899999999999998E-2</v>
+        <v>6.4999999999999997E-3</v>
       </c>
       <c r="N16" s="2">
-        <v>0.60240000000000005</v>
+        <v>0.3659</v>
       </c>
       <c r="O16" s="2">
         <v>1</v>
       </c>
       <c r="P16">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R16" s="2">
-        <v>6.4000000000000003E-3</v>
+        <v>2.4400000000000002E-2</v>
       </c>
       <c r="S16" s="2">
-        <v>3.2300000000000002E-2</v>
-      </c>
-      <c r="T16">
-        <v>21922.042372881355</v>
+        <v>0</v>
+      </c>
+      <c r="T16" s="3">
+        <v>11016.101694915254</v>
       </c>
       <c r="U16" s="3">
-        <v>12869.01</v>
+        <v>0</v>
       </c>
       <c r="V16">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W16">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="B17" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="C17" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="D17" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="E17" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="F17">
-        <v>113</v>
+        <v>506</v>
       </c>
       <c r="G17">
-        <v>3</v>
+        <v>45</v>
       </c>
       <c r="H17" s="2">
-        <v>1.6999999999999999E-3</v>
+        <v>7.7999999999999996E-3</v>
       </c>
       <c r="I17" s="2">
-        <v>1.6000000000000001E-3</v>
+        <v>2.3800000000000002E-2</v>
       </c>
       <c r="J17">
-        <v>164</v>
+        <v>601</v>
       </c>
       <c r="K17">
-        <v>3</v>
+        <v>59</v>
       </c>
       <c r="L17" s="2">
-        <v>1.8E-3</v>
+        <v>6.7000000000000002E-3</v>
       </c>
       <c r="M17" s="2">
-        <v>1.1999999999999999E-3</v>
+        <v>2.2599999999999999E-2</v>
       </c>
       <c r="N17" s="2">
-        <v>0.86899999999999999</v>
+        <v>0.56510000000000005</v>
       </c>
       <c r="O17" s="2">
         <v>1</v>
@@ -2071,13 +2101,13 @@
         <v>0</v>
       </c>
       <c r="R17" s="2">
-        <v>8.8000000000000005E-3</v>
+        <v>2E-3</v>
       </c>
       <c r="S17" s="2">
         <v>0</v>
       </c>
-      <c r="T17">
-        <v>10168.644067796611</v>
+      <c r="T17" s="3">
+        <v>6029.6610169491532</v>
       </c>
       <c r="U17" s="3">
         <v>0</v>
@@ -2091,70 +2121,70 @@
     </row>
     <row r="18" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="B18" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="C18" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="D18" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="E18" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="F18">
-        <v>41</v>
+        <v>256</v>
       </c>
       <c r="G18">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H18" s="2">
-        <v>5.9999999999999995E-4</v>
+        <v>3.8999999999999998E-3</v>
       </c>
       <c r="I18" s="2">
-        <v>5.3E-3</v>
+        <v>3.7000000000000002E-3</v>
       </c>
       <c r="J18">
-        <v>67</v>
+        <v>325</v>
       </c>
       <c r="K18">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="L18" s="2">
-        <v>6.9999999999999999E-4</v>
+        <v>3.5999999999999999E-3</v>
       </c>
       <c r="M18" s="2">
-        <v>6.4999999999999997E-3</v>
+        <v>3.0999999999999999E-3</v>
       </c>
       <c r="N18" s="2">
-        <v>0.3659</v>
+        <v>0.15359999999999999</v>
       </c>
       <c r="O18" s="2">
         <v>1</v>
       </c>
       <c r="P18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q18">
         <v>0</v>
       </c>
       <c r="R18" s="2">
-        <v>2.4400000000000002E-2</v>
+        <v>0</v>
       </c>
       <c r="S18" s="2">
         <v>0</v>
       </c>
-      <c r="T18">
-        <v>11016.101694915254</v>
+      <c r="T18" s="3">
+        <v>0</v>
       </c>
       <c r="U18" s="3">
         <v>0</v>
       </c>
       <c r="V18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W18">
         <v>0</v>
@@ -2162,120 +2192,120 @@
     </row>
     <row r="19" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="B19" t="s">
-        <v>126</v>
+        <v>151</v>
       </c>
       <c r="C19" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="D19" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="E19" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="F19">
-        <v>506</v>
+        <v>524</v>
       </c>
       <c r="G19">
-        <v>45</v>
+        <v>33</v>
       </c>
       <c r="H19" s="2">
-        <v>7.7999999999999996E-3</v>
+        <v>8.0999999999999996E-3</v>
       </c>
       <c r="I19" s="2">
-        <v>2.3800000000000002E-2</v>
+        <v>1.7399999999999999E-2</v>
       </c>
       <c r="J19">
-        <v>601</v>
+        <v>589</v>
       </c>
       <c r="K19">
-        <v>59</v>
+        <v>35</v>
       </c>
       <c r="L19" s="2">
-        <v>6.7000000000000002E-3</v>
+        <v>6.6E-3</v>
       </c>
       <c r="M19" s="2">
-        <v>2.2599999999999999E-2</v>
+        <v>1.34E-2</v>
       </c>
       <c r="N19" s="2">
-        <v>0.56510000000000005</v>
+        <v>0.50739999999999996</v>
       </c>
       <c r="O19" s="2">
         <v>1</v>
       </c>
       <c r="P19">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q19">
         <v>0</v>
       </c>
       <c r="R19" s="2">
-        <v>2E-3</v>
+        <v>0</v>
       </c>
       <c r="S19" s="2">
         <v>0</v>
       </c>
-      <c r="T19">
-        <v>6029.6610169491532</v>
+      <c r="T19" s="3">
+        <v>0</v>
       </c>
       <c r="U19" s="3">
         <v>0</v>
       </c>
       <c r="V19">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W19">
         <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A20" t="s">
-        <v>127</v>
-      </c>
-      <c r="B20" t="s">
-        <v>128</v>
+      <c r="A20" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="B20" t="e">
+        <v>#N/A</v>
       </c>
       <c r="C20" t="s">
-        <v>57</v>
+        <v>152</v>
       </c>
       <c r="D20" t="s">
-        <v>57</v>
+        <v>152</v>
       </c>
       <c r="E20" t="s">
-        <v>58</v>
+        <v>153</v>
       </c>
       <c r="F20">
-        <v>256</v>
+        <v>5</v>
       </c>
       <c r="G20">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="H20" s="2">
-        <v>3.8999999999999998E-3</v>
+        <v>1E-4</v>
       </c>
       <c r="I20" s="2">
-        <v>3.7000000000000002E-3</v>
+        <v>0</v>
       </c>
       <c r="J20">
-        <v>325</v>
+        <v>6</v>
       </c>
       <c r="K20">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="L20" s="2">
-        <v>3.5999999999999999E-3</v>
+        <v>1E-4</v>
       </c>
       <c r="M20" s="2">
-        <v>3.0999999999999999E-3</v>
+        <v>0</v>
       </c>
       <c r="N20" s="2">
-        <v>0.15359999999999999</v>
+        <v>0</v>
       </c>
       <c r="O20" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P20">
         <v>0</v>
@@ -2289,7 +2319,7 @@
       <c r="S20" s="2">
         <v>0</v>
       </c>
-      <c r="T20">
+      <c r="T20" s="3">
         <v>0</v>
       </c>
       <c r="U20" s="3">
@@ -2303,50 +2333,50 @@
       </c>
     </row>
     <row r="21" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A21" t="s">
-        <v>129</v>
-      </c>
-      <c r="B21" t="s">
-        <v>130</v>
+      <c r="A21" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="B21" t="e">
+        <v>#N/A</v>
       </c>
       <c r="C21" t="s">
-        <v>59</v>
+        <v>154</v>
       </c>
       <c r="D21" t="s">
-        <v>59</v>
+        <v>154</v>
       </c>
       <c r="E21" t="s">
-        <v>60</v>
+        <v>155</v>
       </c>
       <c r="F21">
-        <v>524</v>
+        <v>2</v>
       </c>
       <c r="G21">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="H21" s="2">
-        <v>8.0999999999999996E-3</v>
+        <v>0</v>
       </c>
       <c r="I21" s="2">
-        <v>1.7399999999999999E-2</v>
+        <v>0</v>
       </c>
       <c r="J21">
-        <v>589</v>
+        <v>2</v>
       </c>
       <c r="K21">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="L21" s="2">
-        <v>6.6E-3</v>
+        <v>0</v>
       </c>
       <c r="M21" s="2">
-        <v>1.34E-2</v>
+        <v>0</v>
       </c>
       <c r="N21" s="2">
-        <v>0.50739999999999996</v>
+        <v>0</v>
       </c>
       <c r="O21" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P21">
         <v>0</v>
@@ -2360,7 +2390,7 @@
       <c r="S21" s="2">
         <v>0</v>
       </c>
-      <c r="T21">
+      <c r="T21" s="3">
         <v>0</v>
       </c>
       <c r="U21" s="3">
@@ -2375,851 +2405,851 @@
     </row>
     <row r="22" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>131</v>
+        <v>91</v>
       </c>
       <c r="B22" t="s">
-        <v>132</v>
+        <v>92</v>
       </c>
       <c r="C22" t="s">
-        <v>61</v>
+        <v>21</v>
       </c>
       <c r="D22" t="s">
-        <v>61</v>
+        <v>21</v>
       </c>
       <c r="E22" t="s">
-        <v>62</v>
+        <v>22</v>
       </c>
       <c r="F22" s="4">
-        <v>1647</v>
+        <v>5875</v>
       </c>
       <c r="G22">
-        <v>106</v>
+        <v>272</v>
       </c>
       <c r="H22" s="2">
-        <v>2.8E-3</v>
+        <v>8.3000000000000001E-3</v>
       </c>
       <c r="I22" s="2">
-        <v>9.5999999999999992E-3</v>
+        <v>1.9699999999999999E-2</v>
       </c>
       <c r="J22" s="4">
-        <v>2634</v>
+        <v>8037</v>
       </c>
       <c r="K22">
-        <v>177</v>
+        <v>358</v>
       </c>
       <c r="L22" s="2">
-        <v>3.3999999999999998E-3</v>
+        <v>8.3999999999999995E-3</v>
       </c>
       <c r="M22" s="2">
-        <v>1.1900000000000001E-2</v>
+        <v>1.8599999999999998E-2</v>
       </c>
       <c r="N22" s="2">
-        <v>0.99870000000000003</v>
+        <v>2.0999999999999999E-3</v>
       </c>
       <c r="O22" s="2">
-        <v>0.99160000000000004</v>
+        <v>4.0000000000000001E-3</v>
       </c>
       <c r="P22">
-        <v>151</v>
+        <v>0</v>
       </c>
       <c r="Q22">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="R22" s="2">
-        <v>9.1700000000000004E-2</v>
+        <v>0</v>
       </c>
       <c r="S22" s="2">
-        <v>8.4900000000000003E-2</v>
-      </c>
-      <c r="T22">
-        <v>75757.627118644072</v>
+        <v>0</v>
+      </c>
+      <c r="T22" s="3">
+        <v>0</v>
       </c>
       <c r="U22" s="3">
-        <v>5481</v>
+        <v>0</v>
       </c>
       <c r="V22">
-        <v>146</v>
+        <v>0</v>
       </c>
       <c r="W22">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>133</v>
+        <v>93</v>
       </c>
       <c r="B23" t="s">
-        <v>134</v>
+        <v>94</v>
       </c>
       <c r="C23" t="s">
-        <v>63</v>
+        <v>23</v>
       </c>
       <c r="D23" t="s">
-        <v>63</v>
+        <v>23</v>
       </c>
       <c r="E23" t="s">
-        <v>64</v>
+        <v>24</v>
       </c>
       <c r="F23" s="4">
-        <v>2044</v>
+        <v>1595</v>
       </c>
       <c r="G23">
-        <v>111</v>
+        <v>122</v>
       </c>
       <c r="H23" s="2">
-        <v>3.5000000000000001E-3</v>
+        <v>2.2000000000000001E-3</v>
       </c>
       <c r="I23" s="2">
-        <v>1.01E-2</v>
+        <v>8.8000000000000005E-3</v>
       </c>
       <c r="J23" s="4">
-        <v>2963</v>
+        <v>2072</v>
       </c>
       <c r="K23">
-        <v>163</v>
+        <v>154</v>
       </c>
       <c r="L23" s="2">
-        <v>3.8E-3</v>
+        <v>2.2000000000000001E-3</v>
       </c>
       <c r="M23" s="2">
-        <v>1.09E-2</v>
+        <v>8.0000000000000002E-3</v>
       </c>
       <c r="N23" s="2">
-        <v>0.99890000000000001</v>
+        <v>2.2000000000000001E-3</v>
       </c>
       <c r="O23" s="2">
-        <v>1</v>
+        <v>9.5999999999999992E-3</v>
       </c>
       <c r="P23">
-        <v>103</v>
+        <v>0</v>
       </c>
       <c r="Q23">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="R23" s="2">
-        <v>5.04E-2</v>
+        <v>0</v>
       </c>
       <c r="S23" s="2">
-        <v>0.12609999999999999</v>
-      </c>
-      <c r="T23">
-        <v>43477.118644067799</v>
+        <v>0</v>
+      </c>
+      <c r="T23" s="3">
+        <v>0</v>
       </c>
       <c r="U23" s="3">
-        <v>7536</v>
+        <v>0</v>
       </c>
       <c r="V23">
-        <v>95</v>
+        <v>0</v>
       </c>
       <c r="W23">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A24" t="s">
-        <v>135</v>
-      </c>
-      <c r="B24" t="s">
-        <v>136</v>
+      <c r="A24" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="B24" t="e">
+        <v>#N/A</v>
       </c>
       <c r="C24" t="s">
-        <v>65</v>
+        <v>156</v>
       </c>
       <c r="D24" t="s">
-        <v>65</v>
+        <v>156</v>
       </c>
       <c r="E24" t="s">
-        <v>66</v>
-      </c>
-      <c r="F24" s="4">
-        <v>2204</v>
+        <v>157</v>
+      </c>
+      <c r="F24">
+        <v>4</v>
       </c>
       <c r="G24">
-        <v>160</v>
+        <v>0</v>
       </c>
       <c r="H24" s="2">
-        <v>3.8E-3</v>
+        <v>0</v>
       </c>
       <c r="I24" s="2">
-        <v>1.46E-2</v>
-      </c>
-      <c r="J24" s="4">
-        <v>3274</v>
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>5</v>
       </c>
       <c r="K24">
-        <v>224</v>
+        <v>0</v>
       </c>
       <c r="L24" s="2">
-        <v>4.1999999999999997E-3</v>
+        <v>0</v>
       </c>
       <c r="M24" s="2">
-        <v>1.4999999999999999E-2</v>
+        <v>0</v>
       </c>
       <c r="N24" s="2">
-        <v>0.99960000000000004</v>
+        <v>0</v>
       </c>
       <c r="O24" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P24">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="Q24">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="R24" s="2">
-        <v>1.95E-2</v>
+        <v>0</v>
       </c>
       <c r="S24" s="2">
-        <v>4.3799999999999999E-2</v>
-      </c>
-      <c r="T24">
-        <v>93645.423728813563</v>
+        <v>0</v>
+      </c>
+      <c r="T24" s="3">
+        <v>0</v>
       </c>
       <c r="U24" s="3">
-        <v>18786.900000000001</v>
+        <v>0</v>
       </c>
       <c r="V24">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="W24">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>137</v>
+        <v>158</v>
       </c>
       <c r="B25" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="C25" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="D25" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="E25" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="F25" s="4">
-        <v>1160</v>
+        <v>1647</v>
       </c>
       <c r="G25">
-        <v>83</v>
+        <v>106</v>
       </c>
       <c r="H25" s="2">
-        <v>2E-3</v>
+        <v>2.8E-3</v>
       </c>
       <c r="I25" s="2">
-        <v>7.4999999999999997E-3</v>
+        <v>9.5999999999999992E-3</v>
       </c>
       <c r="J25" s="4">
-        <v>1537</v>
+        <v>2634</v>
       </c>
       <c r="K25">
-        <v>100</v>
+        <v>177</v>
       </c>
       <c r="L25" s="2">
-        <v>2E-3</v>
+        <v>3.3999999999999998E-3</v>
       </c>
       <c r="M25" s="2">
-        <v>6.7000000000000002E-3</v>
+        <v>1.1900000000000001E-2</v>
       </c>
       <c r="N25" s="2">
-        <v>0.99860000000000004</v>
+        <v>0.99870000000000003</v>
       </c>
       <c r="O25" s="2">
-        <v>0.97529999999999994</v>
+        <v>0.99160000000000004</v>
       </c>
       <c r="P25">
-        <v>46</v>
+        <v>151</v>
       </c>
       <c r="Q25">
+        <v>9</v>
+      </c>
+      <c r="R25" s="2">
+        <v>9.1700000000000004E-2</v>
+      </c>
+      <c r="S25" s="2">
+        <v>8.4900000000000003E-2</v>
+      </c>
+      <c r="T25" s="3">
+        <v>75757.627118644072</v>
+      </c>
+      <c r="U25" s="3">
+        <v>5481</v>
+      </c>
+      <c r="V25">
+        <v>146</v>
+      </c>
+      <c r="W25">
         <v>8</v>
-      </c>
-      <c r="R25" s="2">
-        <v>3.9699999999999999E-2</v>
-      </c>
-      <c r="S25" s="2">
-        <v>9.64E-2</v>
-      </c>
-      <c r="T25">
-        <v>29202.542372881358</v>
-      </c>
-      <c r="U25" s="3">
-        <v>6189</v>
-      </c>
-      <c r="V25">
-        <v>42</v>
-      </c>
-      <c r="W25">
-        <v>6</v>
       </c>
     </row>
     <row r="26" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>139</v>
+        <v>159</v>
       </c>
       <c r="B26" t="s">
-        <v>140</v>
+        <v>131</v>
       </c>
       <c r="C26" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="D26" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="E26" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="F26" s="4">
-        <v>2301</v>
+        <v>2044</v>
       </c>
       <c r="G26">
-        <v>140</v>
+        <v>111</v>
       </c>
       <c r="H26" s="2">
-        <v>3.8999999999999998E-3</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="I26" s="2">
-        <v>1.2699999999999999E-2</v>
+        <v>1.01E-2</v>
       </c>
       <c r="J26" s="4">
-        <v>3279</v>
+        <v>2963</v>
       </c>
       <c r="K26">
-        <v>194</v>
+        <v>163</v>
       </c>
       <c r="L26" s="2">
-        <v>4.1999999999999997E-3</v>
+        <v>3.8E-3</v>
       </c>
       <c r="M26" s="2">
-        <v>1.2999999999999999E-2</v>
+        <v>1.09E-2</v>
       </c>
       <c r="N26" s="2">
-        <v>0.41139999999999999</v>
+        <v>0.99890000000000001</v>
       </c>
       <c r="O26" s="2">
-        <v>0.14530000000000001</v>
+        <v>1</v>
       </c>
       <c r="P26">
-        <v>38</v>
+        <v>103</v>
       </c>
       <c r="Q26">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="R26" s="2">
-        <v>1.6500000000000001E-2</v>
+        <v>5.04E-2</v>
       </c>
       <c r="S26" s="2">
-        <v>1.43E-2</v>
-      </c>
-      <c r="T26">
-        <v>64248.305084745763</v>
+        <v>0.12609999999999999</v>
+      </c>
+      <c r="T26" s="3">
+        <v>43477.118644067799</v>
       </c>
       <c r="U26" s="3">
-        <v>4098</v>
+        <v>7536</v>
       </c>
       <c r="V26">
-        <v>38</v>
+        <v>95</v>
       </c>
       <c r="W26">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="27" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>141</v>
+        <v>132</v>
       </c>
       <c r="B27" t="s">
-        <v>142</v>
+        <v>133</v>
       </c>
       <c r="C27" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="D27" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="E27" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="F27" s="4">
-        <v>1301</v>
+        <v>2204</v>
       </c>
       <c r="G27">
-        <v>90</v>
+        <v>160</v>
       </c>
       <c r="H27" s="2">
-        <v>2.2000000000000001E-3</v>
+        <v>3.8E-3</v>
       </c>
       <c r="I27" s="2">
-        <v>8.2000000000000007E-3</v>
+        <v>1.46E-2</v>
       </c>
       <c r="J27" s="4">
-        <v>1738</v>
+        <v>3274</v>
       </c>
       <c r="K27">
-        <v>106</v>
+        <v>224</v>
       </c>
       <c r="L27" s="2">
-        <v>2.2000000000000001E-3</v>
+        <v>4.1999999999999997E-3</v>
       </c>
       <c r="M27" s="2">
-        <v>7.1000000000000004E-3</v>
+        <v>1.4999999999999999E-2</v>
       </c>
       <c r="N27" s="2">
-        <v>0.99929999999999997</v>
+        <v>0.99960000000000004</v>
       </c>
       <c r="O27" s="2">
-        <v>0.98670000000000002</v>
+        <v>1</v>
       </c>
       <c r="P27">
-        <v>29</v>
+        <v>43</v>
       </c>
       <c r="Q27">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="R27" s="2">
-        <v>2.23E-2</v>
+        <v>1.95E-2</v>
       </c>
       <c r="S27" s="2">
-        <v>4.4400000000000002E-2</v>
-      </c>
-      <c r="T27">
-        <v>51585.593220338989</v>
+        <v>4.3799999999999999E-2</v>
+      </c>
+      <c r="T27" s="3">
+        <v>93645.423728813563</v>
       </c>
       <c r="U27" s="3">
-        <v>8396</v>
+        <v>18786.900000000001</v>
       </c>
       <c r="V27">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="W27">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="28" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>143</v>
+        <v>160</v>
       </c>
       <c r="B28" t="s">
-        <v>144</v>
+        <v>134</v>
       </c>
       <c r="C28" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="D28" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="E28" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="F28" s="4">
-        <v>1478</v>
+        <v>1160</v>
       </c>
       <c r="G28">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="H28" s="2">
-        <v>2.5000000000000001E-3</v>
+        <v>2E-3</v>
       </c>
       <c r="I28" s="2">
-        <v>8.0000000000000002E-3</v>
+        <v>7.4999999999999997E-3</v>
       </c>
       <c r="J28" s="4">
-        <v>2019</v>
+        <v>1537</v>
       </c>
       <c r="K28">
-        <v>129</v>
+        <v>100</v>
       </c>
       <c r="L28" s="2">
-        <v>2.5999999999999999E-3</v>
+        <v>2E-3</v>
       </c>
       <c r="M28" s="2">
-        <v>8.6999999999999994E-3</v>
+        <v>6.7000000000000002E-3</v>
       </c>
       <c r="N28" s="2">
-        <v>0.6079</v>
+        <v>0.99860000000000004</v>
       </c>
       <c r="O28" s="2">
-        <v>0.623</v>
+        <v>0.97529999999999994</v>
       </c>
       <c r="P28">
-        <v>19</v>
+        <v>46</v>
       </c>
       <c r="Q28">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="R28" s="2">
-        <v>1.29E-2</v>
+        <v>3.9699999999999999E-2</v>
       </c>
       <c r="S28" s="2">
-        <v>1.14E-2</v>
-      </c>
-      <c r="T28">
-        <v>73385.847457627126</v>
+        <v>9.64E-2</v>
+      </c>
+      <c r="T28" s="3">
+        <v>29202.542372881358</v>
       </c>
       <c r="U28" s="3">
-        <v>4849</v>
+        <v>6189</v>
       </c>
       <c r="V28">
-        <v>19</v>
+        <v>42</v>
       </c>
       <c r="W28">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="29" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>145</v>
+        <v>135</v>
       </c>
       <c r="B29" t="s">
-        <v>146</v>
+        <v>136</v>
       </c>
       <c r="C29" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="D29" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="E29" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="F29" s="4">
-        <v>1232</v>
+        <v>2301</v>
       </c>
       <c r="G29">
-        <v>56</v>
+        <v>140</v>
       </c>
       <c r="H29" s="2">
-        <v>2.0999999999999999E-3</v>
+        <v>3.8999999999999998E-3</v>
       </c>
       <c r="I29" s="2">
-        <v>5.1000000000000004E-3</v>
+        <v>1.2699999999999999E-2</v>
       </c>
       <c r="J29" s="4">
-        <v>1666</v>
+        <v>3279</v>
       </c>
       <c r="K29">
-        <v>69</v>
+        <v>194</v>
       </c>
       <c r="L29" s="2">
-        <v>2.0999999999999999E-3</v>
+        <v>4.1999999999999997E-3</v>
       </c>
       <c r="M29" s="2">
-        <v>4.5999999999999999E-3</v>
+        <v>1.2999999999999999E-2</v>
       </c>
       <c r="N29" s="2">
-        <v>0.94369999999999998</v>
+        <v>0.41139999999999999</v>
       </c>
       <c r="O29" s="2">
-        <v>0.78049999999999997</v>
+        <v>0.14530000000000001</v>
       </c>
       <c r="P29">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="Q29">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R29" s="2">
-        <v>1.2999999999999999E-2</v>
+        <v>1.6500000000000001E-2</v>
       </c>
       <c r="S29" s="2">
-        <v>0</v>
-      </c>
-      <c r="T29">
-        <v>22359.322033898305</v>
+        <v>1.43E-2</v>
+      </c>
+      <c r="T29" s="3">
+        <v>64248.305084745763</v>
       </c>
       <c r="U29" s="3">
-        <v>0</v>
+        <v>4098</v>
       </c>
       <c r="V29">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="W29">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="30" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>91</v>
+        <v>161</v>
       </c>
       <c r="B30" t="s">
-        <v>92</v>
+        <v>137</v>
       </c>
       <c r="C30" t="s">
-        <v>21</v>
+        <v>71</v>
       </c>
       <c r="D30" t="s">
-        <v>21</v>
+        <v>71</v>
       </c>
       <c r="E30" t="s">
-        <v>22</v>
+        <v>72</v>
       </c>
       <c r="F30" s="4">
-        <v>5875</v>
+        <v>1301</v>
       </c>
       <c r="G30">
-        <v>272</v>
+        <v>90</v>
       </c>
       <c r="H30" s="2">
-        <v>0.01</v>
+        <v>2.2000000000000001E-3</v>
       </c>
       <c r="I30" s="2">
-        <v>2.47E-2</v>
+        <v>8.2000000000000007E-3</v>
       </c>
       <c r="J30" s="4">
-        <v>8037</v>
+        <v>1738</v>
       </c>
       <c r="K30">
-        <v>358</v>
+        <v>106</v>
       </c>
       <c r="L30" s="2">
-        <v>1.04E-2</v>
+        <v>2.2000000000000001E-3</v>
       </c>
       <c r="M30" s="2">
-        <v>2.4E-2</v>
+        <v>7.1000000000000004E-3</v>
       </c>
       <c r="N30" s="2">
-        <v>8.7499999999999994E-2</v>
+        <v>0.99929999999999997</v>
       </c>
       <c r="O30" s="2">
-        <v>5.16E-2</v>
+        <v>0.98670000000000002</v>
       </c>
       <c r="P30">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="Q30">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R30" s="2">
-        <v>2.2000000000000001E-3</v>
+        <v>2.23E-2</v>
       </c>
       <c r="S30" s="2">
-        <v>0</v>
-      </c>
-      <c r="T30">
-        <v>28294.91525423729</v>
+        <v>4.4400000000000002E-2</v>
+      </c>
+      <c r="T30" s="3">
+        <v>51585.593220338989</v>
       </c>
       <c r="U30" s="3">
-        <v>0</v>
+        <v>8396</v>
       </c>
       <c r="V30">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="W30">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="31" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>147</v>
+        <v>138</v>
       </c>
       <c r="B31" t="s">
-        <v>148</v>
+        <v>139</v>
       </c>
       <c r="C31" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="D31" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="E31" t="s">
-        <v>78</v>
-      </c>
-      <c r="F31">
-        <v>239</v>
+        <v>74</v>
+      </c>
+      <c r="F31" s="4">
+        <v>1478</v>
       </c>
       <c r="G31">
-        <v>27</v>
+        <v>88</v>
       </c>
       <c r="H31" s="2">
-        <v>4.0000000000000002E-4</v>
+        <v>2.5000000000000001E-3</v>
       </c>
       <c r="I31" s="2">
-        <v>2.5000000000000001E-3</v>
-      </c>
-      <c r="J31">
-        <v>322</v>
+        <v>8.0000000000000002E-3</v>
+      </c>
+      <c r="J31" s="4">
+        <v>2019</v>
       </c>
       <c r="K31">
-        <v>35</v>
+        <v>129</v>
       </c>
       <c r="L31" s="2">
-        <v>4.0000000000000002E-4</v>
+        <v>2.5999999999999999E-3</v>
       </c>
       <c r="M31" s="2">
-        <v>2.3E-3</v>
+        <v>8.6999999999999994E-3</v>
       </c>
       <c r="N31" s="2">
-        <v>1</v>
+        <v>0.6079</v>
       </c>
       <c r="O31" s="2">
-        <v>1</v>
+        <v>0.623</v>
       </c>
       <c r="P31">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="Q31">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R31" s="2">
-        <v>4.5999999999999999E-2</v>
+        <v>1.29E-2</v>
       </c>
       <c r="S31" s="2">
-        <v>0</v>
-      </c>
-      <c r="T31">
-        <v>18634.745762711864</v>
+        <v>1.14E-2</v>
+      </c>
+      <c r="T31" s="3">
+        <v>73385.847457627126</v>
       </c>
       <c r="U31" s="3">
-        <v>0</v>
+        <v>4849</v>
       </c>
       <c r="V31">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="W31">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="B32" t="s">
-        <v>150</v>
+        <v>141</v>
       </c>
       <c r="C32" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="D32" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="E32" t="s">
-        <v>80</v>
-      </c>
-      <c r="F32">
-        <v>602</v>
+        <v>76</v>
+      </c>
+      <c r="F32" s="4">
+        <v>1232</v>
       </c>
       <c r="G32">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="H32" s="2">
-        <v>1E-3</v>
+        <v>2.0999999999999999E-3</v>
       </c>
       <c r="I32" s="2">
-        <v>4.4000000000000003E-3</v>
-      </c>
-      <c r="J32">
-        <v>903</v>
+        <v>5.1000000000000004E-3</v>
+      </c>
+      <c r="J32" s="4">
+        <v>1666</v>
       </c>
       <c r="K32">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="L32" s="2">
-        <v>1.1999999999999999E-3</v>
+        <v>2.0999999999999999E-3</v>
       </c>
       <c r="M32" s="2">
-        <v>4.3E-3</v>
+        <v>4.5999999999999999E-3</v>
       </c>
       <c r="N32" s="2">
-        <v>0.67430000000000001</v>
+        <v>0.94369999999999998</v>
       </c>
       <c r="O32" s="2">
-        <v>0.68420000000000003</v>
+        <v>0.78049999999999997</v>
       </c>
       <c r="P32">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="Q32">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R32" s="2">
-        <v>1.66E-2</v>
+        <v>1.2999999999999999E-2</v>
       </c>
       <c r="S32" s="2">
-        <v>2.0799999999999999E-2</v>
-      </c>
-      <c r="T32">
-        <v>15246.610169491527</v>
+        <v>0</v>
+      </c>
+      <c r="T32" s="3">
+        <v>22359.322033898305</v>
       </c>
       <c r="U32" s="3">
-        <v>1999</v>
+        <v>0</v>
       </c>
       <c r="V32">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="W32">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>151</v>
+        <v>91</v>
       </c>
       <c r="B33" t="s">
-        <v>152</v>
+        <v>92</v>
       </c>
       <c r="C33" t="s">
-        <v>81</v>
+        <v>21</v>
       </c>
       <c r="D33" t="s">
-        <v>81</v>
+        <v>21</v>
       </c>
       <c r="E33" t="s">
-        <v>82</v>
+        <v>22</v>
       </c>
       <c r="F33" s="4">
-        <v>5541</v>
+        <v>5875</v>
       </c>
       <c r="G33">
-        <v>360</v>
+        <v>272</v>
       </c>
       <c r="H33" s="2">
-        <v>9.4000000000000004E-3</v>
+        <v>0.01</v>
       </c>
       <c r="I33" s="2">
-        <v>3.27E-2</v>
+        <v>2.47E-2</v>
       </c>
       <c r="J33" s="4">
-        <v>7814</v>
+        <v>8037</v>
       </c>
       <c r="K33">
-        <v>478</v>
+        <v>358</v>
       </c>
       <c r="L33" s="2">
-        <v>1.01E-2</v>
+        <v>1.04E-2</v>
       </c>
       <c r="M33" s="2">
-        <v>3.2099999999999997E-2</v>
+        <v>2.4E-2</v>
       </c>
       <c r="N33" s="2">
-        <v>3.6499999999999998E-2</v>
+        <v>8.7499999999999994E-2</v>
       </c>
       <c r="O33" s="2">
-        <v>3.3999999999999998E-3</v>
+        <v>5.16E-2</v>
       </c>
       <c r="P33">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="Q33">
         <v>0</v>
       </c>
       <c r="R33" s="2">
-        <v>1.4E-3</v>
+        <v>2.2000000000000001E-3</v>
       </c>
       <c r="S33" s="2">
         <v>0</v>
       </c>
-      <c r="T33">
-        <v>20247.457627118645</v>
+      <c r="T33" s="3">
+        <v>28294.91525423729</v>
       </c>
       <c r="U33" s="3">
         <v>0</v>
       </c>
       <c r="V33">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="W33">
         <v>0</v>
@@ -3227,43 +3257,43 @@
     </row>
     <row r="34" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="B34" t="s">
-        <v>154</v>
+        <v>142</v>
       </c>
       <c r="C34" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="D34" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="E34" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="F34">
-        <v>214</v>
+        <v>239</v>
       </c>
       <c r="G34">
-        <v>6</v>
+        <v>27</v>
       </c>
       <c r="H34" s="2">
         <v>4.0000000000000002E-4</v>
       </c>
       <c r="I34" s="2">
-        <v>5.0000000000000001E-4</v>
+        <v>2.5000000000000001E-3</v>
       </c>
       <c r="J34">
-        <v>273</v>
+        <v>322</v>
       </c>
       <c r="K34">
-        <v>9</v>
+        <v>35</v>
       </c>
       <c r="L34" s="2">
         <v>4.0000000000000002E-4</v>
       </c>
       <c r="M34" s="2">
-        <v>5.9999999999999995E-4</v>
+        <v>2.3E-3</v>
       </c>
       <c r="N34" s="2">
         <v>1</v>
@@ -3272,167 +3302,167 @@
         <v>1</v>
       </c>
       <c r="P34">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="Q34">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R34" s="2">
-        <v>3.27E-2</v>
+        <v>4.5999999999999999E-2</v>
       </c>
       <c r="S34" s="2">
-        <v>0.33329999999999999</v>
-      </c>
-      <c r="T34">
-        <v>4244.9152542372885</v>
+        <v>0</v>
+      </c>
+      <c r="T34" s="3">
+        <v>18634.745762711864</v>
       </c>
       <c r="U34" s="3">
-        <v>1078</v>
+        <v>0</v>
       </c>
       <c r="V34">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="W34">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>95</v>
+        <v>143</v>
       </c>
       <c r="B35" t="s">
-        <v>96</v>
+        <v>144</v>
       </c>
       <c r="C35" t="s">
-        <v>25</v>
+        <v>79</v>
       </c>
       <c r="D35" t="s">
-        <v>25</v>
+        <v>79</v>
       </c>
       <c r="E35" t="s">
-        <v>26</v>
-      </c>
-      <c r="F35" s="4">
-        <v>1470</v>
+        <v>80</v>
+      </c>
+      <c r="F35">
+        <v>602</v>
       </c>
       <c r="G35">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="H35" s="2">
-        <v>2.5000000000000001E-3</v>
+        <v>1E-3</v>
       </c>
       <c r="I35" s="2">
-        <v>4.0000000000000001E-3</v>
-      </c>
-      <c r="J35" s="4">
-        <v>2098</v>
+        <v>4.4000000000000003E-3</v>
+      </c>
+      <c r="J35">
+        <v>903</v>
       </c>
       <c r="K35">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="L35" s="2">
-        <v>2.7000000000000001E-3</v>
+        <v>1.1999999999999999E-3</v>
       </c>
       <c r="M35" s="2">
-        <v>4.0000000000000001E-3</v>
+        <v>4.3E-3</v>
       </c>
       <c r="N35" s="2">
-        <v>0.14929999999999999</v>
+        <v>0.67430000000000001</v>
       </c>
       <c r="O35" s="2">
-        <v>2.5600000000000001E-2</v>
+        <v>0.68420000000000003</v>
       </c>
       <c r="P35">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="Q35">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R35" s="2">
-        <v>6.9999999999999999E-4</v>
+        <v>1.66E-2</v>
       </c>
       <c r="S35" s="2">
-        <v>0</v>
-      </c>
-      <c r="T35">
-        <v>0</v>
+        <v>2.0799999999999999E-2</v>
+      </c>
+      <c r="T35" s="3">
+        <v>15246.610169491527</v>
       </c>
       <c r="U35" s="3">
-        <v>0</v>
+        <v>1999</v>
       </c>
       <c r="V35">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="W35">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="36" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>155</v>
+        <v>145</v>
       </c>
       <c r="B36" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
       <c r="C36" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="D36" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="E36" t="s">
-        <v>86</v>
-      </c>
-      <c r="F36">
-        <v>84</v>
+        <v>82</v>
+      </c>
+      <c r="F36" s="4">
+        <v>5541</v>
       </c>
       <c r="G36">
-        <v>7</v>
+        <v>360</v>
       </c>
       <c r="H36" s="2">
-        <v>1E-4</v>
+        <v>9.4000000000000004E-3</v>
       </c>
       <c r="I36" s="2">
-        <v>5.9999999999999995E-4</v>
-      </c>
-      <c r="J36">
-        <v>144</v>
+        <v>3.27E-2</v>
+      </c>
+      <c r="J36" s="4">
+        <v>7814</v>
       </c>
       <c r="K36">
-        <v>9</v>
+        <v>478</v>
       </c>
       <c r="L36" s="2">
-        <v>2.0000000000000001E-4</v>
+        <v>1.01E-2</v>
       </c>
       <c r="M36" s="2">
-        <v>5.9999999999999995E-4</v>
+        <v>3.2099999999999997E-2</v>
       </c>
       <c r="N36" s="2">
-        <v>1</v>
+        <v>3.6499999999999998E-2</v>
       </c>
       <c r="O36" s="2">
-        <v>0.4</v>
+        <v>3.3999999999999998E-3</v>
       </c>
       <c r="P36">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="Q36">
         <v>0</v>
       </c>
       <c r="R36" s="2">
-        <v>1.1900000000000001E-2</v>
+        <v>1.4E-3</v>
       </c>
       <c r="S36" s="2">
         <v>0</v>
       </c>
-      <c r="T36">
-        <v>4660.1694915254238</v>
+      <c r="T36" s="3">
+        <v>20247.457627118645</v>
       </c>
       <c r="U36" s="3">
         <v>0</v>
       </c>
       <c r="V36">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="W36">
         <v>0</v>
@@ -3440,143 +3470,569 @@
     </row>
     <row r="37" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>93</v>
+        <v>147</v>
       </c>
       <c r="B37" t="s">
-        <v>94</v>
+        <v>148</v>
       </c>
       <c r="C37" t="s">
-        <v>23</v>
+        <v>83</v>
       </c>
       <c r="D37" t="s">
-        <v>23</v>
+        <v>83</v>
       </c>
       <c r="E37" t="s">
-        <v>24</v>
-      </c>
-      <c r="F37" s="4">
-        <v>1595</v>
+        <v>84</v>
+      </c>
+      <c r="F37">
+        <v>214</v>
       </c>
       <c r="G37">
-        <v>122</v>
+        <v>6</v>
       </c>
       <c r="H37" s="2">
-        <v>2.7000000000000001E-3</v>
+        <v>4.0000000000000002E-4</v>
       </c>
       <c r="I37" s="2">
-        <v>1.11E-2</v>
-      </c>
-      <c r="J37" s="4">
-        <v>2072</v>
+        <v>5.0000000000000001E-4</v>
+      </c>
+      <c r="J37">
+        <v>273</v>
       </c>
       <c r="K37">
-        <v>154</v>
+        <v>9</v>
       </c>
       <c r="L37" s="2">
-        <v>2.7000000000000001E-3</v>
+        <v>4.0000000000000002E-4</v>
       </c>
       <c r="M37" s="2">
-        <v>1.03E-2</v>
+        <v>5.9999999999999995E-4</v>
       </c>
       <c r="N37" s="2">
-        <v>2.35E-2</v>
+        <v>1</v>
       </c>
       <c r="O37" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P37">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="Q37">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R37" s="2">
-        <v>0</v>
+        <v>3.27E-2</v>
       </c>
       <c r="S37" s="2">
-        <v>0</v>
-      </c>
-      <c r="T37">
-        <v>0</v>
+        <v>0.33329999999999999</v>
+      </c>
+      <c r="T37" s="3">
+        <v>4244.9152542372885</v>
       </c>
       <c r="U37" s="3">
-        <v>0</v>
+        <v>1078</v>
       </c>
       <c r="V37">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="W37">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="38" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
+        <v>95</v>
+      </c>
+      <c r="B38" t="s">
+        <v>96</v>
+      </c>
+      <c r="C38" t="s">
+        <v>25</v>
+      </c>
+      <c r="D38" t="s">
+        <v>25</v>
+      </c>
+      <c r="E38" t="s">
+        <v>26</v>
+      </c>
+      <c r="F38" s="4">
+        <v>1470</v>
+      </c>
+      <c r="G38">
+        <v>44</v>
+      </c>
+      <c r="H38" s="2">
+        <v>2.5000000000000001E-3</v>
+      </c>
+      <c r="I38" s="2">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="J38" s="4">
+        <v>2098</v>
+      </c>
+      <c r="K38">
+        <v>59</v>
+      </c>
+      <c r="L38" s="2">
+        <v>2.7000000000000001E-3</v>
+      </c>
+      <c r="M38" s="2">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="N38" s="2">
+        <v>0.14929999999999999</v>
+      </c>
+      <c r="O38" s="2">
+        <v>2.5600000000000001E-2</v>
+      </c>
+      <c r="P38">
+        <v>1</v>
+      </c>
+      <c r="Q38">
+        <v>0</v>
+      </c>
+      <c r="R38" s="2">
+        <v>6.9999999999999999E-4</v>
+      </c>
+      <c r="S38" s="2">
+        <v>0</v>
+      </c>
+      <c r="T38" s="3">
+        <v>0</v>
+      </c>
+      <c r="U38" s="3">
+        <v>0</v>
+      </c>
+      <c r="V38">
+        <v>1</v>
+      </c>
+      <c r="W38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
+        <v>163</v>
+      </c>
+      <c r="B39" t="s">
+        <v>149</v>
+      </c>
+      <c r="C39" t="s">
+        <v>85</v>
+      </c>
+      <c r="D39" t="s">
+        <v>85</v>
+      </c>
+      <c r="E39" t="s">
+        <v>86</v>
+      </c>
+      <c r="F39">
+        <v>84</v>
+      </c>
+      <c r="G39">
+        <v>7</v>
+      </c>
+      <c r="H39" s="2">
+        <v>1E-4</v>
+      </c>
+      <c r="I39" s="2">
+        <v>5.9999999999999995E-4</v>
+      </c>
+      <c r="J39">
+        <v>144</v>
+      </c>
+      <c r="K39">
+        <v>9</v>
+      </c>
+      <c r="L39" s="2">
+        <v>2.0000000000000001E-4</v>
+      </c>
+      <c r="M39" s="2">
+        <v>5.9999999999999995E-4</v>
+      </c>
+      <c r="N39" s="2">
+        <v>1</v>
+      </c>
+      <c r="O39" s="2">
+        <v>0.4</v>
+      </c>
+      <c r="P39">
+        <v>1</v>
+      </c>
+      <c r="Q39">
+        <v>0</v>
+      </c>
+      <c r="R39" s="2">
+        <v>1.1900000000000001E-2</v>
+      </c>
+      <c r="S39" s="2">
+        <v>0</v>
+      </c>
+      <c r="T39" s="3">
+        <v>4660.1694915254238</v>
+      </c>
+      <c r="U39" s="3">
+        <v>0</v>
+      </c>
+      <c r="V39">
+        <v>1</v>
+      </c>
+      <c r="W39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
+        <v>93</v>
+      </c>
+      <c r="B40" t="s">
+        <v>94</v>
+      </c>
+      <c r="C40" t="s">
+        <v>23</v>
+      </c>
+      <c r="D40" t="s">
+        <v>23</v>
+      </c>
+      <c r="E40" t="s">
+        <v>24</v>
+      </c>
+      <c r="F40" s="4">
+        <v>1595</v>
+      </c>
+      <c r="G40">
+        <v>122</v>
+      </c>
+      <c r="H40" s="2">
+        <v>2.7000000000000001E-3</v>
+      </c>
+      <c r="I40" s="2">
+        <v>1.11E-2</v>
+      </c>
+      <c r="J40" s="4">
+        <v>2072</v>
+      </c>
+      <c r="K40">
+        <v>154</v>
+      </c>
+      <c r="L40" s="2">
+        <v>2.7000000000000001E-3</v>
+      </c>
+      <c r="M40" s="2">
+        <v>1.03E-2</v>
+      </c>
+      <c r="N40" s="2">
+        <v>2.35E-2</v>
+      </c>
+      <c r="O40" s="2">
+        <v>0</v>
+      </c>
+      <c r="P40">
+        <v>0</v>
+      </c>
+      <c r="Q40">
+        <v>0</v>
+      </c>
+      <c r="R40" s="2">
+        <v>0</v>
+      </c>
+      <c r="S40" s="2">
+        <v>0</v>
+      </c>
+      <c r="T40" s="3">
+        <v>0</v>
+      </c>
+      <c r="U40" s="3">
+        <v>0</v>
+      </c>
+      <c r="V40">
+        <v>0</v>
+      </c>
+      <c r="W40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A41" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="B41" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="C41" t="s">
+        <v>156</v>
+      </c>
+      <c r="D41" t="s">
+        <v>156</v>
+      </c>
+      <c r="E41" t="s">
         <v>157</v>
       </c>
-      <c r="B38" t="s">
-        <v>158</v>
-      </c>
-      <c r="C38" t="s">
+      <c r="F41">
+        <v>4</v>
+      </c>
+      <c r="G41">
+        <v>0</v>
+      </c>
+      <c r="H41" s="2">
+        <v>0</v>
+      </c>
+      <c r="I41" s="2">
+        <v>0</v>
+      </c>
+      <c r="J41">
+        <v>5</v>
+      </c>
+      <c r="K41">
+        <v>0</v>
+      </c>
+      <c r="L41" s="2">
+        <v>0</v>
+      </c>
+      <c r="M41" s="2">
+        <v>0</v>
+      </c>
+      <c r="N41" s="2">
+        <v>0</v>
+      </c>
+      <c r="O41" s="2">
+        <v>0</v>
+      </c>
+      <c r="P41">
+        <v>0</v>
+      </c>
+      <c r="Q41">
+        <v>0</v>
+      </c>
+      <c r="R41" s="2">
+        <v>0</v>
+      </c>
+      <c r="S41" s="2">
+        <v>0</v>
+      </c>
+      <c r="T41" s="3">
+        <v>0</v>
+      </c>
+      <c r="U41" s="3">
+        <v>0</v>
+      </c>
+      <c r="V41">
+        <v>0</v>
+      </c>
+      <c r="W41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A42" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="B42" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="C42" t="s">
+        <v>164</v>
+      </c>
+      <c r="D42" t="s">
+        <v>164</v>
+      </c>
+      <c r="E42" t="s">
+        <v>165</v>
+      </c>
+      <c r="F42">
+        <v>1</v>
+      </c>
+      <c r="G42">
+        <v>0</v>
+      </c>
+      <c r="H42" s="2">
+        <v>0</v>
+      </c>
+      <c r="I42" s="2">
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <v>1</v>
+      </c>
+      <c r="K42">
+        <v>0</v>
+      </c>
+      <c r="L42" s="2">
+        <v>0</v>
+      </c>
+      <c r="M42" s="2">
+        <v>0</v>
+      </c>
+      <c r="N42" s="2">
+        <v>0</v>
+      </c>
+      <c r="O42" s="2">
+        <v>0</v>
+      </c>
+      <c r="P42">
+        <v>0</v>
+      </c>
+      <c r="Q42">
+        <v>0</v>
+      </c>
+      <c r="R42" s="2">
+        <v>0</v>
+      </c>
+      <c r="S42" s="2">
+        <v>0</v>
+      </c>
+      <c r="T42" s="3">
+        <v>0</v>
+      </c>
+      <c r="U42" s="3">
+        <v>0</v>
+      </c>
+      <c r="V42">
+        <v>0</v>
+      </c>
+      <c r="W42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
+        <v>166</v>
+      </c>
+      <c r="B43" t="s">
+        <v>150</v>
+      </c>
+      <c r="C43" t="s">
         <v>87</v>
       </c>
-      <c r="D38" t="s">
+      <c r="D43" t="s">
         <v>87</v>
       </c>
-      <c r="E38" t="s">
+      <c r="E43" t="s">
         <v>88</v>
       </c>
-      <c r="F38">
+      <c r="F43">
         <v>38</v>
       </c>
-      <c r="G38">
+      <c r="G43">
         <v>7</v>
       </c>
-      <c r="H38" s="2">
+      <c r="H43" s="2">
         <v>1E-4</v>
       </c>
-      <c r="I38" s="2">
+      <c r="I43" s="2">
         <v>5.9999999999999995E-4</v>
       </c>
-      <c r="J38">
+      <c r="J43">
         <v>47</v>
       </c>
-      <c r="K38">
+      <c r="K43">
         <v>8</v>
       </c>
-      <c r="L38" s="2">
+      <c r="L43" s="2">
         <v>1E-4</v>
       </c>
-      <c r="M38" s="2">
+      <c r="M43" s="2">
         <v>5.0000000000000001E-4</v>
       </c>
-      <c r="N38" s="2">
+      <c r="N43" s="2">
         <v>0.97499999999999998</v>
       </c>
-      <c r="O38" s="2">
+      <c r="O43" s="2">
         <v>0.75</v>
       </c>
-      <c r="P38">
-        <v>0</v>
-      </c>
-      <c r="Q38">
-        <v>0</v>
-      </c>
-      <c r="R38" s="2">
-        <v>0</v>
-      </c>
-      <c r="S38" s="2">
-        <v>0</v>
-      </c>
-      <c r="T38">
-        <v>0</v>
-      </c>
-      <c r="U38" s="3">
-        <v>0</v>
-      </c>
-      <c r="V38">
-        <v>0</v>
-      </c>
-      <c r="W38">
+      <c r="P43">
+        <v>0</v>
+      </c>
+      <c r="Q43">
+        <v>0</v>
+      </c>
+      <c r="R43" s="2">
+        <v>0</v>
+      </c>
+      <c r="S43" s="2">
+        <v>0</v>
+      </c>
+      <c r="T43" s="3">
+        <v>0</v>
+      </c>
+      <c r="U43" s="3">
+        <v>0</v>
+      </c>
+      <c r="V43">
+        <v>0</v>
+      </c>
+      <c r="W43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A44" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="B44" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="C44" t="s">
+        <v>167</v>
+      </c>
+      <c r="D44" t="s">
+        <v>167</v>
+      </c>
+      <c r="E44" t="s">
+        <v>168</v>
+      </c>
+      <c r="F44">
+        <v>2</v>
+      </c>
+      <c r="G44">
+        <v>0</v>
+      </c>
+      <c r="H44" s="2">
+        <v>0</v>
+      </c>
+      <c r="I44" s="2">
+        <v>0</v>
+      </c>
+      <c r="J44">
+        <v>4</v>
+      </c>
+      <c r="K44">
+        <v>0</v>
+      </c>
+      <c r="L44" s="2">
+        <v>0</v>
+      </c>
+      <c r="M44" s="2">
+        <v>0</v>
+      </c>
+      <c r="N44" s="2">
+        <v>0</v>
+      </c>
+      <c r="O44" s="2">
+        <v>0</v>
+      </c>
+      <c r="P44">
+        <v>0</v>
+      </c>
+      <c r="Q44">
+        <v>0</v>
+      </c>
+      <c r="R44" s="2">
+        <v>0</v>
+      </c>
+      <c r="S44" s="2">
+        <v>0</v>
+      </c>
+      <c r="T44" s="3">
+        <v>0</v>
+      </c>
+      <c r="U44" s="3">
+        <v>0</v>
+      </c>
+      <c r="V44">
+        <v>0</v>
+      </c>
+      <c r="W44">
         <v>0</v>
       </c>
     </row>
